--- a/astro-site/public/dl/fine-dining-checklist-templates/04-kitchen-brigade-duties-by-role.xlsx
+++ b/astro-site/public/dl/fine-dining-checklist-templates/04-kitchen-brigade-duties-by-role.xlsx
@@ -1471,7 +1471,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Main cooking: proteins, hot sides</t>
+          <t>Main cooking: proteins, hot sides; hot food held at 135 °F or above (FDA Food Code 3-501.16) — log reading: ____ °F</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Manage sous vide during service (rethermalize, sear)</t>
+          <t>Manage sous vide during service (rethermalize, sear): cooked-and-chilled food reheated to 165 °F within 2 hr for hot holding (FDA Food Code 3-403.11); hold hot food at 135 °F or above (3-501.16)</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
